--- a/data/dividends_info_20260404.xlsx
+++ b/data/dividends_info_20260404.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K146"/>
+  <dimension ref="A1:K166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.12</v>
+        <v>0.297</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>20.55999946594238</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I98" t="n">
-        <v>5.447470958621759</v>
+        <v>3.986577283272386</v>
       </c>
       <c r="J98" t="n">
         <v>44</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1.25</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>0.7462686661585043</v>
       </c>
       <c r="J99" t="n">
         <v>44</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0003865570</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2.384000062942505</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I100" t="n">
-        <v>10.90603998051448</v>
+        <v>0.7782101369459655</v>
       </c>
       <c r="J100" t="n">
         <v>44</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.013999938964844</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="I101" t="n">
-        <v>4.582919701945988</v>
+        <v>3.34394908521068</v>
       </c>
       <c r="J101" t="n">
         <v>44</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5219,30 +5219,30 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>9.359999656677246</v>
+        <v>1.5</v>
       </c>
       <c r="I102" t="n">
-        <v>3.739316376473546</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J102" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K102" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.096</v>
+        <v>0.38</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5266,44 +5266,44 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>4.599999904632568</v>
+        <v>18.25</v>
       </c>
       <c r="I103" t="n">
-        <v>2.086956565006019</v>
+        <v>2.082191780821918</v>
       </c>
       <c r="J103" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K103" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5313,30 +5313,30 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.800000190734863</v>
+        <v>25.28000068664551</v>
       </c>
       <c r="I104" t="n">
-        <v>5.172413623006964</v>
+        <v>2.373417657053142</v>
       </c>
       <c r="J104" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K104" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5345,12 +5345,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5360,30 +5360,30 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>11.80000019073486</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="I105" t="n">
-        <v>1.694915226840727</v>
+        <v>1.118210889876268</v>
       </c>
       <c r="J105" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K105" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.06</v>
+        <v>0.017</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5392,45 +5392,45 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>9.060000419616699</v>
+        <v>3.065000057220459</v>
       </c>
       <c r="I106" t="n">
-        <v>0.6622516249567504</v>
+        <v>0.5546492555506412</v>
       </c>
       <c r="J106" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K106" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5454,30 +5454,30 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2.140000104904175</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="I107" t="n">
-        <v>2.803738180315963</v>
+        <v>0.3533568999855096</v>
       </c>
       <c r="J107" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K107" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5</v>
+        <v>1.12</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5486,12 +5486,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5501,26 +5501,26 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>15.46000003814697</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="I108" t="n">
-        <v>3.234152644025023</v>
+        <v>5.447470958621759</v>
       </c>
       <c r="J108" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K108" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5548,30 +5548,30 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.880000114440918</v>
+        <v>1.25</v>
       </c>
       <c r="I109" t="n">
-        <v>2.577319511610616</v>
+        <v>8</v>
       </c>
       <c r="J109" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K109" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5595,30 +5595,30 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>IT0003865570</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>9.399999618530273</v>
+        <v>2.384000062942505</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9042553558453239</v>
+        <v>10.90603998051448</v>
       </c>
       <c r="J110" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K110" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.095</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5642,30 +5642,30 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>4.46999979019165</v>
+        <v>2.013999938964844</v>
       </c>
       <c r="I111" t="n">
-        <v>2.125279741812402</v>
+        <v>4.582919701945988</v>
       </c>
       <c r="J111" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K111" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1.110000014305115</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="I112" t="n">
-        <v>2.702702667871647</v>
+        <v>3.739316376473546</v>
       </c>
       <c r="J112" t="n">
         <v>37</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.09</v>
+        <v>0.096</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>7.75</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="I113" t="n">
-        <v>1.161290322580645</v>
+        <v>2.086956565006019</v>
       </c>
       <c r="J113" t="n">
         <v>37</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>7.400000095367432</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I114" t="n">
-        <v>1.351351333935824</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J114" t="n">
         <v>37</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>7</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I115" t="n">
-        <v>3.142857142857143</v>
+        <v>1.694915226840727</v>
       </c>
       <c r="J115" t="n">
         <v>37</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5862,45 +5862,45 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0004093263</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>3.470000028610229</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I116" t="n">
-        <v>4.610950970628137</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J116" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K116" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.61</v>
+        <v>0.06</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5924,30 +5924,30 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>21.95000076293945</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I117" t="n">
-        <v>2.779043183588078</v>
+        <v>2.803738180315963</v>
       </c>
       <c r="J117" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K117" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5971,30 +5971,30 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>2.960000038146973</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="I118" t="n">
-        <v>5.067567502259338</v>
+        <v>3.234152644025023</v>
       </c>
       <c r="J118" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K118" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6018,30 +6018,30 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>11.85000038146973</v>
+        <v>3.880000114440918</v>
       </c>
       <c r="I119" t="n">
-        <v>5.907172805619612</v>
+        <v>2.577319511610616</v>
       </c>
       <c r="J119" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K119" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5105</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6065,44 +6065,44 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005545238</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>8.829999923706055</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I120" t="n">
-        <v>5.78142700352071</v>
+        <v>0.9042553558453239</v>
       </c>
       <c r="J120" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K120" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.27</v>
+        <v>0.095</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6112,30 +6112,30 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>7.949999809265137</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="I121" t="n">
-        <v>3.396226496575949</v>
+        <v>2.125279741812402</v>
       </c>
       <c r="J121" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K121" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.35</v>
+        <v>0.03</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6159,30 +6159,30 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>5.090000152587891</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="I122" t="n">
-        <v>6.876227691703521</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J122" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K122" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6206,30 +6206,30 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>37.20000076293945</v>
+        <v>7.75</v>
       </c>
       <c r="I123" t="n">
-        <v>2.956989186666567</v>
+        <v>1.161290322580645</v>
       </c>
       <c r="J123" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K123" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6238,45 +6238,45 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>18.70000076293945</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I124" t="n">
-        <v>4.010695023533825</v>
+        <v>1.351351333935824</v>
       </c>
       <c r="J124" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K124" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6300,30 +6300,30 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>26.79999923706055</v>
+        <v>7</v>
       </c>
       <c r="I125" t="n">
-        <v>1.119403016941669</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="J125" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K125" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.007</v>
+        <v>0.16</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6347,30 +6347,30 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0001073045</t>
+          <t>IT0004093263</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>0.1529999971389771</v>
+        <v>3.470000028610229</v>
       </c>
       <c r="I126" t="n">
-        <v>4.575163484246064</v>
+        <v>4.610950970628137</v>
       </c>
       <c r="J126" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K126" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.16</v>
+        <v>0.61</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6394,30 +6394,30 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>6.650000095367432</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="I127" t="n">
-        <v>2.406015003089403</v>
+        <v>2.779043183588078</v>
       </c>
       <c r="J127" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K127" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.065</v>
+        <v>0.15</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6441,30 +6441,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.214999914169312</v>
+        <v>2.960000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>2.93453735976224</v>
+        <v>5.067567502259338</v>
       </c>
       <c r="J128" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K128" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6488,30 +6488,30 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>7.46999979019165</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="I129" t="n">
-        <v>3.346720308188737</v>
+        <v>5.907172805619612</v>
       </c>
       <c r="J129" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K129" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5105</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6535,44 +6535,44 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005549255</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1.379999995231628</v>
+        <v>8.829999923706055</v>
       </c>
       <c r="I130" t="n">
-        <v>5.072463785643038</v>
+        <v>5.78142700352071</v>
       </c>
       <c r="J130" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K130" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6582,30 +6582,30 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>6.639999866485596</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="I131" t="n">
-        <v>7.530120633340297</v>
+        <v>3.396226496575949</v>
       </c>
       <c r="J131" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K131" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6629,30 +6629,30 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0004776628</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>17.72999954223633</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="I132" t="n">
-        <v>3.666102745527843</v>
+        <v>6.876227691703521</v>
       </c>
       <c r="J132" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K132" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6676,30 +6676,30 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>12.05000019073486</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="I133" t="n">
-        <v>4.481327729896645</v>
+        <v>2.956989186666567</v>
       </c>
       <c r="J133" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K133" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6708,45 +6708,45 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>6.245999813079834</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="I134" t="n">
-        <v>1.601024703692572</v>
+        <v>4.010695023533825</v>
       </c>
       <c r="J134" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K134" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6770,30 +6770,30 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>8.319999694824219</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I135" t="n">
-        <v>1.923076993614967</v>
+        <v>4.134615536272179</v>
       </c>
       <c r="J135" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K135" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3.615</v>
+        <v>0.15</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6817,30 +6817,30 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>NL0011585146</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>295.5</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I136" t="n">
-        <v>1.223350253807107</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J136" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K136" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1.36</v>
+        <v>0.197169</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6864,30 +6864,30 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005144784</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>27</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="I137" t="n">
-        <v>5.037037037037037</v>
+        <v>1.60299997514244</v>
       </c>
       <c r="J137" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K137" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.585</v>
+        <v>1.1</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6911,30 +6911,30 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0004931058</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>13.84000015258789</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I138" t="n">
-        <v>4.226878566114849</v>
+        <v>4.10447772878612</v>
       </c>
       <c r="J138" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K138" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6943,12 +6943,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6958,30 +6958,30 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0000062957</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>16.53499984741211</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I139" t="n">
-        <v>3.810099823488061</v>
+        <v>2.659574576015658</v>
       </c>
       <c r="J139" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K139" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.9</v>
+        <v>0.47</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7005,30 +7005,30 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0004176001</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>104.6999969482422</v>
+        <v>40.54999923706055</v>
       </c>
       <c r="I140" t="n">
-        <v>0.8595988789234726</v>
+        <v>1.159062907134274</v>
       </c>
       <c r="J140" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K140" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1.7208</v>
+        <v>0.11</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7052,30 +7052,30 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0005239360</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>62.65999984741211</v>
+        <v>2.450000047683716</v>
       </c>
       <c r="I141" t="n">
-        <v>2.746249607708976</v>
+        <v>4.489795830983613</v>
       </c>
       <c r="J141" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K141" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.14</v>
+        <v>1.2</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7099,30 +7099,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0001214433</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>23</v>
+        <v>78.59999847412109</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6086956521739131</v>
+        <v>1.526717586890409</v>
       </c>
       <c r="J142" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K142" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.06</v>
+        <v>0.27</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0005418204</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1.480000019073486</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="I143" t="n">
-        <v>4.05405400180747</v>
+        <v>1.158798321205706</v>
       </c>
       <c r="J143" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K143" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.034</v>
+        <v>0.38</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,30 +7193,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>IT0005379604</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1.889999985694885</v>
+        <v>10.25</v>
       </c>
       <c r="I144" t="n">
-        <v>1.798941812557709</v>
+        <v>3.707317073170731</v>
       </c>
       <c r="J144" t="n">
-        <v>-5</v>
+        <v>30</v>
       </c>
       <c r="K144" t="n">
-        <v>-3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7225,81 +7225,1021 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>24.68499946594238</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I145" t="n">
-        <v>1.053271240125887</v>
+        <v>1.119403016941669</v>
       </c>
       <c r="J145" t="n">
-        <v>-12</v>
+        <v>30</v>
       </c>
       <c r="K145" t="n">
-        <v>-10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>Banca Profilo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>IT0001073045</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0.1529999971389771</v>
+      </c>
+      <c r="I146" t="n">
+        <v>4.575163484246064</v>
+      </c>
+      <c r="J146" t="n">
+        <v>23</v>
+      </c>
+      <c r="K146" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>IT0001033700</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>6.650000095367432</v>
+      </c>
+      <c r="I147" t="n">
+        <v>2.406015003089403</v>
+      </c>
+      <c r="J147" t="n">
+        <v>23</v>
+      </c>
+      <c r="K147" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>EDISON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>IT0003372205</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>2.214999914169312</v>
+      </c>
+      <c r="I148" t="n">
+        <v>2.93453735976224</v>
+      </c>
+      <c r="J148" t="n">
+        <v>23</v>
+      </c>
+      <c r="K148" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Fiera Milano S.p.A</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>IT0003365613</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="I149" t="n">
+        <v>3.346720308188737</v>
+      </c>
+      <c r="J149" t="n">
+        <v>23</v>
+      </c>
+      <c r="K149" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>IT0005549255</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>1.379999995231628</v>
+      </c>
+      <c r="I150" t="n">
+        <v>5.072463785643038</v>
+      </c>
+      <c r="J150" t="n">
+        <v>23</v>
+      </c>
+      <c r="K150" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Anima Holding S.p.A.</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>IT0004998065</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>6.639999866485596</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7.530120633340297</v>
+      </c>
+      <c r="J151" t="n">
+        <v>16</v>
+      </c>
+      <c r="K151" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>IT0004776628</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>17.72999954223633</v>
+      </c>
+      <c r="I152" t="n">
+        <v>3.666102745527843</v>
+      </c>
+      <c r="J152" t="n">
+        <v>16</v>
+      </c>
+      <c r="K152" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Banco BPM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>IT0005218380</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>12.05000019073486</v>
+      </c>
+      <c r="I153" t="n">
+        <v>4.481327729896645</v>
+      </c>
+      <c r="J153" t="n">
+        <v>16</v>
+      </c>
+      <c r="K153" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>NL0015435975</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>6.245999813079834</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1.601024703692572</v>
+      </c>
+      <c r="J154" t="n">
+        <v>16</v>
+      </c>
+      <c r="K154" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>IT0005215329</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>8.319999694824219</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1.923076993614967</v>
+      </c>
+      <c r="J155" t="n">
+        <v>16</v>
+      </c>
+      <c r="K155" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>NL0011585146</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>295.5</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1.223350253807107</v>
+      </c>
+      <c r="J156" t="n">
+        <v>16</v>
+      </c>
+      <c r="K156" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>IT0005144784</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>27</v>
+      </c>
+      <c r="I157" t="n">
+        <v>5.037037037037037</v>
+      </c>
+      <c r="J157" t="n">
+        <v>16</v>
+      </c>
+      <c r="K157" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>IT0004931058</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>13.84000015258789</v>
+      </c>
+      <c r="I158" t="n">
+        <v>4.226878566114849</v>
+      </c>
+      <c r="J158" t="n">
+        <v>16</v>
+      </c>
+      <c r="K158" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>IT0000062957</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>16.53499984741211</v>
+      </c>
+      <c r="I159" t="n">
+        <v>3.810099823488061</v>
+      </c>
+      <c r="J159" t="n">
+        <v>16</v>
+      </c>
+      <c r="K159" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>IT0004176001</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>104.6999969482422</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.8595988789234726</v>
+      </c>
+      <c r="J160" t="n">
+        <v>16</v>
+      </c>
+      <c r="K160" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1.7208</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>IT0005239360</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>62.65999984741211</v>
+      </c>
+      <c r="I161" t="n">
+        <v>2.746249607708976</v>
+      </c>
+      <c r="J161" t="n">
+        <v>16</v>
+      </c>
+      <c r="K161" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>IT0001214433</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>23</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="J162" t="n">
+        <v>9</v>
+      </c>
+      <c r="K162" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Reti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>IT0005418204</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1.480000019073486</v>
+      </c>
+      <c r="I163" t="n">
+        <v>4.05405400180747</v>
+      </c>
+      <c r="J163" t="n">
+        <v>9</v>
+      </c>
+      <c r="K163" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Confinvest F.L. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>IT0005379604</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>1.889999985694885</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1.798941812557709</v>
+      </c>
+      <c r="J164" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Eni S.p.A.</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>IT0003132476</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>24.68499946594238</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1.053271240125887</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>STMicroelectronics N.V.</t>
         </is>
       </c>
-      <c r="B146" t="n">
+      <c r="B166" t="n">
         <v>0.09</v>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>DOLLARI USA</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Interim</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H146" t="n">
+      <c r="H166" t="n">
         <v>29.08499908447266</v>
       </c>
-      <c r="I146" t="n">
+      <c r="I166" t="n">
         <v>0.309437864304584</v>
       </c>
-      <c r="J146" t="n">
+      <c r="J166" t="n">
         <v>-12</v>
       </c>
-      <c r="K146" t="n">
+      <c r="K166" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -7314,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C421"/>
+  <dimension ref="A1:C441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7558,7 +8498,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7568,7 +8508,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -7592,7 +8532,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7602,7 +8542,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -7660,7 +8600,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7670,14 +8610,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7687,14 +8627,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7711,7 +8651,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7721,14 +8661,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7745,7 +8685,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7755,7 +8695,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -7772,14 +8712,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7789,14 +8729,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7806,14 +8746,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7823,14 +8763,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7840,14 +8780,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7864,7 +8804,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7874,14 +8814,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7891,14 +8831,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7908,14 +8848,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7925,14 +8865,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7949,7 +8889,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7966,7 +8906,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7976,14 +8916,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7993,14 +8933,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8034,7 +8974,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8044,14 +8984,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8061,14 +9001,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8078,14 +9018,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8102,7 +9042,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8112,14 +9052,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8129,7 +9069,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8238,7 +9178,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8255,7 +9195,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8265,14 +9205,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8289,7 +9229,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8306,7 +9246,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8316,14 +9256,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8357,7 +9297,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8374,7 +9314,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8384,14 +9324,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8408,7 +9348,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8418,7 +9358,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8527,7 +9467,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8537,7 +9477,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8561,7 +9501,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8571,14 +9511,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8663,7 +9603,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8673,14 +9613,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8690,19 +9630,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8714,29 +9654,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8748,46 +9688,46 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8799,29 +9739,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -8833,12 +9773,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -8850,7 +9790,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8867,7 +9807,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8877,14 +9817,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8901,7 +9841,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8918,7 +9858,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8928,14 +9868,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8952,7 +9892,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8962,14 +9902,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8979,14 +9919,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9003,7 +9943,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9020,7 +9960,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9037,12 +9977,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9054,12 +9994,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9071,12 +10011,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9088,12 +10028,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9105,12 +10045,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9122,29 +10062,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9156,29 +10096,29 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9190,12 +10130,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9207,7 +10147,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9224,7 +10164,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9241,7 +10181,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9258,7 +10198,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9275,7 +10215,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9292,7 +10232,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9309,7 +10249,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9326,7 +10266,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9343,7 +10283,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9360,7 +10300,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9377,7 +10317,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9394,7 +10334,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9411,7 +10351,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9421,14 +10361,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9445,7 +10385,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9462,7 +10402,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9472,14 +10412,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9496,7 +10436,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9513,7 +10453,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9530,7 +10470,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9547,12 +10487,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9564,97 +10504,97 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9666,29 +10606,29 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9700,12 +10640,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9717,7 +10657,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9734,7 +10674,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9744,14 +10684,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9761,14 +10701,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9785,7 +10725,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9795,14 +10735,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9819,7 +10759,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9836,7 +10776,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9853,7 +10793,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9863,14 +10803,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9880,36 +10820,36 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9921,29 +10861,29 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9955,12 +10895,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9972,29 +10912,29 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10006,12 +10946,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10023,12 +10963,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10040,24 +10980,24 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10074,7 +11014,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10084,14 +11024,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10108,7 +11048,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10125,7 +11065,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10142,7 +11082,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10159,7 +11099,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10176,7 +11116,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10193,7 +11133,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10210,7 +11150,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10227,7 +11167,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10244,7 +11184,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10261,7 +11201,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10278,7 +11218,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10295,7 +11235,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10305,14 +11245,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10329,7 +11269,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10346,7 +11286,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10363,7 +11303,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10380,7 +11320,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10397,7 +11337,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10407,14 +11347,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10431,12 +11371,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10448,12 +11388,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10465,12 +11405,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10482,46 +11422,46 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10533,12 +11473,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10550,12 +11490,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10567,12 +11507,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10584,12 +11524,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10601,7 +11541,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10618,7 +11558,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10635,7 +11575,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10645,14 +11585,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10669,7 +11609,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10686,7 +11626,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10703,7 +11643,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10720,7 +11660,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10737,7 +11677,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10754,7 +11694,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10771,7 +11711,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10781,14 +11721,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10805,7 +11745,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -10822,7 +11762,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -10839,7 +11779,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -10856,7 +11796,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -10873,7 +11813,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -10890,7 +11830,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -10907,7 +11847,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -10924,7 +11864,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -10941,7 +11881,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -10958,7 +11898,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -10975,7 +11915,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -10992,7 +11932,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11002,14 +11942,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11026,7 +11966,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11043,7 +11983,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11053,14 +11993,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11094,7 +12034,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11111,7 +12051,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11128,7 +12068,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11145,7 +12085,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11162,7 +12102,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11179,7 +12119,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -11189,14 +12129,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -11206,14 +12146,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -11230,7 +12170,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -11247,7 +12187,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11264,7 +12204,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11281,7 +12221,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -11298,7 +12238,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -11315,7 +12255,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -11332,7 +12272,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11349,7 +12289,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -11366,7 +12306,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11376,14 +12316,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11400,29 +12340,29 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -11434,12 +12374,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -11451,12 +12391,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -11468,12 +12408,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -11485,29 +12425,29 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11519,12 +12459,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11536,29 +12476,29 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11570,7 +12510,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -11580,14 +12520,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -11604,7 +12544,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -11621,7 +12561,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -11638,7 +12578,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -11655,7 +12595,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -11672,7 +12612,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -11682,14 +12622,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -11706,7 +12646,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -11723,7 +12663,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -11740,7 +12680,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -11757,7 +12697,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -11774,7 +12714,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -11791,7 +12731,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -11808,7 +12748,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -11825,7 +12765,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -11835,14 +12775,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -11859,7 +12799,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -11876,7 +12816,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -11893,7 +12833,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -11910,7 +12850,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -11927,7 +12867,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -11944,7 +12884,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -11961,7 +12901,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -11978,7 +12918,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -11995,7 +12935,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12012,7 +12952,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12029,7 +12969,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -12046,7 +12986,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12056,14 +12996,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -12073,14 +13013,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12090,14 +13030,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -12114,7 +13054,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12131,7 +13071,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12141,14 +13081,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12165,7 +13105,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12182,7 +13122,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12199,7 +13139,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12216,7 +13156,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12226,7 +13166,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12250,7 +13190,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -12267,7 +13207,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -12277,14 +13217,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12301,7 +13241,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -12311,14 +13251,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12335,7 +13275,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -12352,7 +13292,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -12369,7 +13309,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -12386,7 +13326,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -12420,7 +13360,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -12437,7 +13377,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -12454,7 +13394,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -12471,7 +13411,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -12488,7 +13428,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -12505,7 +13445,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -12522,7 +13462,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -12532,14 +13472,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -12556,7 +13496,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -12566,14 +13506,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -12583,14 +13523,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -12600,14 +13540,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -12624,7 +13564,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -12641,7 +13581,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -12658,7 +13598,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -12675,7 +13615,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -12692,7 +13632,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -12709,7 +13649,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -12719,14 +13659,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -12743,7 +13683,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -12760,7 +13700,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -12777,12 +13717,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12794,12 +13734,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12811,12 +13751,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -12828,29 +13768,29 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -12862,29 +13802,29 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12896,46 +13836,46 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12947,46 +13887,46 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12998,29 +13938,29 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -13032,12 +13972,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -13049,12 +13989,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -13066,12 +14006,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13083,12 +14023,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -13100,24 +14040,24 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13134,7 +14074,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13151,7 +14091,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13168,7 +14108,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13185,7 +14125,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -13202,7 +14142,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -13219,7 +14159,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -13236,7 +14176,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -13253,7 +14193,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -13270,7 +14210,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -13287,7 +14227,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -13304,7 +14244,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -13355,7 +14295,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -13372,7 +14312,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -13389,7 +14329,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -13406,7 +14346,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -13416,14 +14356,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -13440,7 +14380,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -13457,7 +14397,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -13474,7 +14414,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -13491,7 +14431,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -13508,7 +14448,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -13525,7 +14465,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -13542,7 +14482,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -13559,7 +14499,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -13576,7 +14516,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -13593,7 +14533,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -13610,7 +14550,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -13627,7 +14567,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -13637,14 +14577,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -13661,7 +14601,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -13678,7 +14618,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -13695,7 +14635,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -13712,7 +14652,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -13729,7 +14669,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -13746,7 +14686,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -13763,7 +14703,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -13780,7 +14720,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -13790,14 +14730,14 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -13814,7 +14754,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -13824,14 +14764,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -13848,7 +14788,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -13865,7 +14805,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -13882,7 +14822,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -13899,7 +14839,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -13916,7 +14856,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -13933,7 +14873,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -13950,7 +14890,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -13967,7 +14907,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -13984,7 +14924,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -14001,7 +14941,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -14011,14 +14951,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -14028,14 +14968,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -14052,7 +14992,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -14069,7 +15009,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -14086,7 +15026,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -14103,7 +15043,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -14120,7 +15060,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -14137,7 +15077,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -14147,36 +15087,36 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14188,12 +15128,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14205,12 +15145,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14222,63 +15162,63 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -14290,63 +15230,63 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -14358,29 +15298,29 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -14392,12 +15332,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -14409,29 +15349,29 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -14443,12 +15383,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -14460,15 +15400,355 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
+          <t>Litix S.p.A.</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>SOGES GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>IRCE s.p.a</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Tecno S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Solid World Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>RISANAMENTO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Nusco S.p.A.</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>NEWPRINCES</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Markbass S.p.A.</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>MARZOCCHI POMPE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>ACQUAZZURRA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Anima Holding S.p.A.</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>DigiTouch S.p.A.</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>EDILIZIACROBATICA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>EuroGroup Laminations S.p.A.</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
           <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B439" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>VALTECNE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Lemon Sistemi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -14498,350 +15778,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACQUAZZURRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anima Holding S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EuroGroup Laminations S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lemon Sistemi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Markbass S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Nusco S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Solid World Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>